--- a/data/source/weekly/cs-en-us-033pct.xlsx
+++ b/data/source/weekly/cs-en-us-033pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -914,17 +914,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
@@ -933,10 +933,10 @@
         <v>1</v>
       </c>
       <c r="J15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
@@ -956,34 +956,34 @@
         <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K16" s="14">
-        <v>87.5</v>
+        <v>45.454545454545</v>
       </c>
       <c r="L16" s="14">
-        <v>-11.764705882352</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="M16" s="14">
-        <v>-37.5</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="N16" s="13" t="s">
         <v>21</v>
@@ -994,37 +994,37 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>800</v>
+        <v>150</v>
       </c>
       <c r="F17" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H17" s="14">
-        <v>108.333333333333</v>
+        <v>136.363636363636</v>
       </c>
       <c r="I17" s="15">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J17" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K17" s="14">
-        <v>89.473684210526</v>
+        <v>100</v>
       </c>
       <c r="L17" s="14">
-        <v>20</v>
+        <v>10.526315789473</v>
       </c>
       <c r="M17" s="14">
-        <v>111.764705882353</v>
+        <v>100</v>
       </c>
       <c r="N17" s="13" t="s">
         <v>21</v>
@@ -1038,34 +1038,34 @@
         <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F18" s="15">
+        <v>8</v>
+      </c>
+      <c r="G18" s="15">
+        <v>7</v>
+      </c>
+      <c r="H18" s="14">
+        <v>14.285714285714</v>
+      </c>
+      <c r="I18" s="15">
+        <v>11</v>
+      </c>
+      <c r="J18" s="15">
+        <v>10</v>
+      </c>
+      <c r="K18" s="14">
+        <v>10</v>
+      </c>
+      <c r="L18" s="14">
+        <v>-31.25</v>
+      </c>
+      <c r="M18" s="14">
         <v>0</v>
-      </c>
-      <c r="F18" s="15">
-        <v>9</v>
-      </c>
-      <c r="G18" s="15">
-        <v>6</v>
-      </c>
-      <c r="H18" s="14">
-        <v>50</v>
-      </c>
-      <c r="I18" s="15">
-        <v>9</v>
-      </c>
-      <c r="J18" s="15">
-        <v>7</v>
-      </c>
-      <c r="K18" s="14">
-        <v>28.571428571428</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-35.714285714285</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-10</v>
       </c>
       <c r="N18" s="13" t="s">
         <v>21</v>
@@ -1076,37 +1076,37 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="14">
-        <v>-66.666666666666</v>
+        <v>20</v>
       </c>
       <c r="F19" s="15">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G19" s="15">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H19" s="14">
-        <v>-18.518518518518</v>
+        <v>-32</v>
       </c>
       <c r="I19" s="15">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J19" s="15">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K19" s="14">
-        <v>-33.333333333333</v>
+        <v>-29.545454545454</v>
       </c>
       <c r="L19" s="14">
-        <v>-10.344827586206</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="M19" s="14">
-        <v>44.444444444444</v>
+        <v>47.619047619047</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>21</v>
@@ -1117,37 +1117,37 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>200</v>
       </c>
       <c r="F20" s="15">
         <v>9</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="I20" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J20" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K20" s="14">
-        <v>20</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L20" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M20" s="14">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N20" s="13" t="s">
         <v>21</v>
@@ -1158,37 +1158,37 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>16</v>
+      </c>
+      <c r="D21" s="17">
         <v>15</v>
       </c>
-      <c r="D21" s="17">
-        <v>10</v>
-      </c>
       <c r="E21" s="18">
-        <v>50</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G21" s="17">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H21" s="18">
-        <v>25.423728813559</v>
+        <v>11.475409836065</v>
       </c>
       <c r="I21" s="17">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="J21" s="17">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="K21" s="18">
-        <v>16.470588235294</v>
+        <v>16</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.883495145631</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="M21" s="18">
-        <v>25.316455696202</v>
+        <v>23.404255319148</v>
       </c>
       <c r="N21" s="19" t="s">
         <v>21</v>
@@ -1211,7 +1211,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="14">
         <v>-100</v>
@@ -1220,7 +1220,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="14">
         <v>-100</v>
@@ -1251,11 +1251,11 @@
       <c r="F23" s="15">
         <v>1</v>
       </c>
-      <c r="G23" s="15">
-        <v>1</v>
-      </c>
-      <c r="H23" s="14">
-        <v>0</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="15">
         <v>2</v>
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M23" s="14">
         <v>0</v>
@@ -1281,34 +1281,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D24" s="15">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E24" s="14">
-        <v>-11.111111111111</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F24" s="15">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G24" s="15">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H24" s="14">
-        <v>-28.378378378378</v>
+        <v>-30.882352941176</v>
       </c>
       <c r="I24" s="15">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="J24" s="15">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="K24" s="14">
-        <v>-22.580645161290</v>
+        <v>-20.754716981132</v>
       </c>
       <c r="L24" s="14">
-        <v>-19.101123595505</v>
+        <v>-16</v>
       </c>
       <c r="M24" s="14">
         <v>100</v>
@@ -1321,32 +1321,32 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>1</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" s="14">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" s="15">
         <v>28</v>
       </c>
       <c r="H25" s="14">
-        <v>-75</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="I25" s="15">
         <v>11</v>
       </c>
       <c r="J25" s="15">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K25" s="14">
-        <v>-65.625</v>
+        <v>-70.270270270270</v>
       </c>
       <c r="L25" s="14">
         <v>0</v>
@@ -1363,37 +1363,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>4</v>
+      </c>
+      <c r="D26" s="15">
+        <v>7</v>
+      </c>
+      <c r="E26" s="14">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="F26" s="15">
+        <v>21</v>
+      </c>
+      <c r="G26" s="15">
+        <v>24</v>
+      </c>
+      <c r="H26" s="14">
+        <v>-12.5</v>
+      </c>
+      <c r="I26" s="15">
+        <v>42</v>
+      </c>
+      <c r="J26" s="15">
+        <v>36</v>
+      </c>
+      <c r="K26" s="14">
+        <v>16.666666666666</v>
+      </c>
+      <c r="L26" s="14">
         <v>5</v>
       </c>
-      <c r="D26" s="15">
-        <v>8</v>
-      </c>
-      <c r="E26" s="14">
-        <v>-37.5</v>
-      </c>
-      <c r="F26" s="15">
-        <v>23</v>
-      </c>
-      <c r="G26" s="15">
-        <v>20</v>
-      </c>
-      <c r="H26" s="14">
-        <v>15</v>
-      </c>
-      <c r="I26" s="15">
-        <v>37</v>
-      </c>
-      <c r="J26" s="15">
-        <v>29</v>
-      </c>
-      <c r="K26" s="14">
-        <v>27.586206896551</v>
-      </c>
-      <c r="L26" s="14">
-        <v>2.777777777777</v>
-      </c>
       <c r="M26" s="14">
-        <v>-21.276595744680</v>
+        <v>-16</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1406,17 +1406,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1425,10 +1425,10 @@
         <v>1</v>
       </c>
       <c r="J27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L27" s="14">
         <v>-50</v>
@@ -1444,35 +1444,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="15">
+        <v>3</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F28" s="15">
         <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="15">
-        <v>2</v>
       </c>
       <c r="G28" s="15">
         <v>7</v>
       </c>
       <c r="H28" s="14">
-        <v>-71.428571428571</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K28" s="14">
-        <v>-75</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-033pct.xlsx
+++ b/data/source/weekly/cs-en-us-033pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -914,17 +914,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="15">
         <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="15">
-        <v>2</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
@@ -939,7 +939,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M15" s="14">
         <v>0</v>
@@ -953,37 +953,37 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
+        <v>3</v>
+      </c>
+      <c r="D16" s="15">
         <v>1</v>
       </c>
-      <c r="D16" s="15">
-        <v>3</v>
-      </c>
       <c r="E16" s="14">
-        <v>-66.666666666666</v>
+        <v>200</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
         <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J16" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K16" s="14">
-        <v>45.454545454545</v>
+        <v>58.333333333333</v>
       </c>
       <c r="L16" s="14">
-        <v>-5.882352941176</v>
+        <v>-5</v>
       </c>
       <c r="M16" s="14">
-        <v>-46.666666666666</v>
+        <v>-44.117647058823</v>
       </c>
       <c r="N16" s="13" t="s">
         <v>21</v>
@@ -994,37 +994,37 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14">
-        <v>150</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F17" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G17" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H17" s="14">
-        <v>136.363636363636</v>
+        <v>107.142857142857</v>
       </c>
       <c r="I17" s="15">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="J17" s="15">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K17" s="14">
-        <v>100</v>
+        <v>82.142857142857</v>
       </c>
       <c r="L17" s="14">
-        <v>10.526315789473</v>
+        <v>27.5</v>
       </c>
       <c r="M17" s="14">
-        <v>100</v>
+        <v>131.818181818182</v>
       </c>
       <c r="N17" s="13" t="s">
         <v>21</v>
@@ -1035,37 +1035,37 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>-66.666666666666</v>
+        <v>300</v>
       </c>
       <c r="F18" s="15">
+        <v>14</v>
+      </c>
+      <c r="G18" s="15">
         <v>8</v>
       </c>
-      <c r="G18" s="15">
-        <v>7</v>
-      </c>
       <c r="H18" s="14">
-        <v>14.285714285714</v>
+        <v>75</v>
       </c>
       <c r="I18" s="15">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J18" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K18" s="14">
-        <v>10</v>
+        <v>58.333333333333</v>
       </c>
       <c r="L18" s="14">
-        <v>-31.25</v>
+        <v>5.555555555555</v>
       </c>
       <c r="M18" s="14">
-        <v>0</v>
+        <v>72.727272727272</v>
       </c>
       <c r="N18" s="13" t="s">
         <v>21</v>
@@ -1076,37 +1076,37 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
         <v>5</v>
       </c>
       <c r="E19" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G19" s="15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H19" s="14">
-        <v>-32</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I19" s="15">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J19" s="15">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K19" s="14">
-        <v>-29.545454545454</v>
+        <v>-26.530612244898</v>
       </c>
       <c r="L19" s="14">
-        <v>-13.888888888888</v>
+        <v>-20</v>
       </c>
       <c r="M19" s="14">
-        <v>47.619047619047</v>
+        <v>50</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>21</v>
@@ -1126,28 +1126,28 @@
         <v>200</v>
       </c>
       <c r="F20" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
         <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J20" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K20" s="14">
-        <v>36.363636363636</v>
+        <v>50</v>
       </c>
       <c r="L20" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M20" s="14">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="N20" s="13" t="s">
         <v>21</v>
@@ -1158,37 +1158,37 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>27</v>
+      </c>
+      <c r="D21" s="17">
         <v>16</v>
       </c>
-      <c r="D21" s="17">
-        <v>15</v>
-      </c>
       <c r="E21" s="18">
-        <v>6.666666666666</v>
+        <v>68.75</v>
       </c>
       <c r="F21" s="17">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G21" s="17">
         <v>61</v>
       </c>
       <c r="H21" s="18">
-        <v>11.475409836065</v>
+        <v>19.672131147541</v>
       </c>
       <c r="I21" s="17">
+        <v>144</v>
+      </c>
+      <c r="J21" s="17">
         <v>116</v>
       </c>
-      <c r="J21" s="17">
-        <v>100</v>
-      </c>
       <c r="K21" s="18">
-        <v>16</v>
+        <v>24.137931034482</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.333333333333</v>
+        <v>2.857142857142</v>
       </c>
       <c r="M21" s="18">
-        <v>23.404255319148</v>
+        <v>41.176470588235</v>
       </c>
       <c r="N21" s="19" t="s">
         <v>21</v>
@@ -1201,11 +1201,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1242,32 +1242,32 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="15">
+      <c r="D23" s="15">
         <v>1</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="14">
+        <v>-100</v>
       </c>
       <c r="I23" s="15">
         <v>2</v>
       </c>
       <c r="J23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L23" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="M23" s="14">
         <v>0</v>
@@ -1281,37 +1281,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D24" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E24" s="14">
-        <v>-7.692307692307</v>
+        <v>-37.5</v>
       </c>
       <c r="F24" s="15">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G24" s="15">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H24" s="14">
-        <v>-30.882352941176</v>
+        <v>-33.870967741935</v>
       </c>
       <c r="I24" s="15">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="J24" s="15">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="K24" s="14">
-        <v>-20.754716981132</v>
+        <v>-23.770491803278</v>
       </c>
       <c r="L24" s="14">
-        <v>-16</v>
+        <v>-17.699115044247</v>
       </c>
       <c r="M24" s="14">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1321,35 +1321,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="15">
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G25" s="15">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H25" s="14">
-        <v>-78.571428571428</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="I25" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J25" s="15">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K25" s="14">
-        <v>-70.270270270270</v>
+        <v>-70</v>
       </c>
       <c r="L25" s="14">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1363,37 +1363,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>-42.857142857142</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15">
         <v>21</v>
       </c>
       <c r="G26" s="15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H26" s="14">
-        <v>-12.5</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="I26" s="15">
+        <v>48</v>
+      </c>
+      <c r="J26" s="15">
         <v>42</v>
       </c>
-      <c r="J26" s="15">
-        <v>36</v>
-      </c>
       <c r="K26" s="14">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L26" s="14">
-        <v>5</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M26" s="14">
-        <v>-16</v>
+        <v>-21.311475409836</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1406,17 +1406,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="15">
         <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="15">
-        <v>2</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1431,7 +1431,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L27" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1447,32 +1447,32 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
-        <v>3</v>
-      </c>
-      <c r="E28" s="14">
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15">
+        <v>2</v>
+      </c>
+      <c r="G28" s="15">
+        <v>6</v>
+      </c>
+      <c r="H28" s="14">
         <v>-66.666666666666</v>
       </c>
-      <c r="F28" s="15">
-        <v>1</v>
-      </c>
-      <c r="G28" s="15">
-        <v>7</v>
-      </c>
-      <c r="H28" s="14">
-        <v>-85.714285714285</v>
-      </c>
       <c r="I28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="15">
         <v>11</v>
       </c>
       <c r="K28" s="14">
-        <v>-72.727272727272</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="L28" s="14">
-        <v>-25</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,8 +1494,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="15">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1516,7 +1516,7 @@
         <v>21</v>
       </c>
       <c r="M29" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N29" s="13" t="s">
         <v>21</v>
@@ -1535,8 +1535,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="15">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1557,7 +1557,7 @@
         <v>21</v>
       </c>
       <c r="M30" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-033pct.xlsx
+++ b/data/source/weekly/cs-en-us-033pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -914,17 +914,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
@@ -933,13 +933,13 @@
         <v>1</v>
       </c>
       <c r="J15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="14">
+        <v>-75</v>
+      </c>
+      <c r="L15" s="14">
         <v>-66.666666666666</v>
-      </c>
-      <c r="L15" s="14">
-        <v>-50</v>
       </c>
       <c r="M15" s="14">
         <v>0</v>
@@ -953,37 +953,37 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
+        <v>12.5</v>
+      </c>
+      <c r="I16" s="15">
+        <v>23</v>
+      </c>
+      <c r="J16" s="15">
+        <v>14</v>
+      </c>
+      <c r="K16" s="14">
+        <v>64.285714285714</v>
+      </c>
+      <c r="L16" s="14">
         <v>0</v>
       </c>
-      <c r="I16" s="15">
-        <v>19</v>
-      </c>
-      <c r="J16" s="15">
-        <v>12</v>
-      </c>
-      <c r="K16" s="14">
-        <v>58.333333333333</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-5</v>
-      </c>
       <c r="M16" s="14">
-        <v>-44.117647058823</v>
+        <v>-36.111111111111</v>
       </c>
       <c r="N16" s="13" t="s">
         <v>21</v>
@@ -994,37 +994,37 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>14.285714285714</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G17" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H17" s="14">
-        <v>107.142857142857</v>
+        <v>68.75</v>
       </c>
       <c r="I17" s="15">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J17" s="15">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K17" s="14">
-        <v>82.142857142857</v>
+        <v>61.764705882352</v>
       </c>
       <c r="L17" s="14">
-        <v>27.5</v>
+        <v>30.952380952381</v>
       </c>
       <c r="M17" s="14">
-        <v>131.818181818182</v>
+        <v>111.538461538462</v>
       </c>
       <c r="N17" s="13" t="s">
         <v>21</v>
@@ -1035,37 +1035,37 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>8</v>
-      </c>
-      <c r="D18" s="15">
-        <v>2</v>
-      </c>
-      <c r="E18" s="14">
-        <v>300</v>
+        <v>1</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G18" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H18" s="14">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="I18" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18" s="15">
         <v>12</v>
       </c>
       <c r="K18" s="14">
-        <v>58.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L18" s="14">
-        <v>5.555555555555</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M18" s="14">
-        <v>72.727272727272</v>
+        <v>42.857142857142</v>
       </c>
       <c r="N18" s="13" t="s">
         <v>21</v>
@@ -1076,37 +1076,37 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G19" s="15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H19" s="14">
-        <v>-33.333333333333</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="I19" s="15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J19" s="15">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K19" s="14">
-        <v>-26.530612244898</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L19" s="14">
-        <v>-20</v>
+        <v>-29.824561403508</v>
       </c>
       <c r="M19" s="14">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>21</v>
@@ -1116,38 +1116,38 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>3</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
         <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="15">
         <v>18</v>
       </c>
       <c r="J20" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K20" s="14">
-        <v>50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L20" s="14">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="M20" s="14">
-        <v>100</v>
+        <v>63.636363636363</v>
       </c>
       <c r="N20" s="13" t="s">
         <v>21</v>
@@ -1158,37 +1158,37 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>68.75</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F21" s="17">
         <v>73</v>
       </c>
       <c r="G21" s="17">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H21" s="18">
-        <v>19.672131147541</v>
+        <v>23.728813559322</v>
       </c>
       <c r="I21" s="17">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="J21" s="17">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="K21" s="18">
-        <v>24.137931034482</v>
+        <v>17.164179104477</v>
       </c>
       <c r="L21" s="18">
-        <v>2.857142857142</v>
+        <v>-4.848484848484</v>
       </c>
       <c r="M21" s="18">
-        <v>41.176470588235</v>
+        <v>30.833333333333</v>
       </c>
       <c r="N21" s="19" t="s">
         <v>21</v>
@@ -1211,7 +1211,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
         <v>-100</v>
@@ -1242,11 +1242,11 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="15">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
@@ -1270,7 +1270,7 @@
         <v>-60</v>
       </c>
       <c r="M23" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1281,37 +1281,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D24" s="15">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E24" s="14">
-        <v>-37.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F24" s="15">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G24" s="15">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="H24" s="14">
-        <v>-33.870967741935</v>
+        <v>-29.729729729729</v>
       </c>
       <c r="I24" s="15">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="J24" s="15">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="K24" s="14">
-        <v>-23.770491803278</v>
+        <v>-27.516778523489</v>
       </c>
       <c r="L24" s="14">
-        <v>-17.699115044247</v>
+        <v>-11.475409836065</v>
       </c>
       <c r="M24" s="14">
-        <v>55</v>
+        <v>56.521739130434</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1325,31 +1325,31 @@
         <v>1</v>
       </c>
       <c r="D25" s="15">
+        <v>9</v>
+      </c>
+      <c r="E25" s="14">
+        <v>-88.888888888888</v>
+      </c>
+      <c r="F25" s="15">
         <v>3</v>
       </c>
-      <c r="E25" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F25" s="15">
-        <v>2</v>
-      </c>
       <c r="G25" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H25" s="14">
-        <v>-88.888888888888</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I25" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J25" s="15">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K25" s="14">
-        <v>-70</v>
+        <v>-73.469387755102</v>
       </c>
       <c r="L25" s="14">
-        <v>-7.692307692307</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1363,37 +1363,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F26" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G26" s="15">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H26" s="14">
-        <v>-8.695652173913</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="J26" s="15">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K26" s="14">
-        <v>14.285714285714</v>
+        <v>7.843137254901</v>
       </c>
       <c r="L26" s="14">
-        <v>9.090909090909</v>
+        <v>5.769230769230</v>
       </c>
       <c r="M26" s="14">
-        <v>-21.311475409836</v>
+        <v>-20.289855072463</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1406,17 +1406,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1425,13 +1425,13 @@
         <v>1</v>
       </c>
       <c r="J27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L27" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1444,8 +1444,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1457,10 +1457,10 @@
         <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="15">
         <v>4</v>
@@ -1472,7 +1472,7 @@
         <v>-63.636363636363</v>
       </c>
       <c r="L28" s="14">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-033pct.xlsx
+++ b/data/source/weekly/cs-en-us-033pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -914,11 +914,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -953,37 +953,37 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="15">
         <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K16" s="14">
-        <v>64.285714285714</v>
+        <v>41.176470588235</v>
       </c>
       <c r="L16" s="14">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M16" s="14">
-        <v>-36.111111111111</v>
+        <v>-35.135135135135</v>
       </c>
       <c r="N16" s="13" t="s">
         <v>21</v>
@@ -994,37 +994,37 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
-      </c>
-      <c r="D17" s="15">
-        <v>6</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-33.333333333333</v>
+        <v>2</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="15">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G17" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H17" s="14">
-        <v>68.75</v>
+        <v>26.666666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J17" s="15">
         <v>34</v>
       </c>
       <c r="K17" s="14">
-        <v>61.764705882352</v>
+        <v>67.647058823529</v>
       </c>
       <c r="L17" s="14">
-        <v>30.952380952381</v>
+        <v>16.326530612244</v>
       </c>
       <c r="M17" s="14">
-        <v>111.538461538462</v>
+        <v>83.870967741935</v>
       </c>
       <c r="N17" s="13" t="s">
         <v>21</v>
@@ -1035,37 +1035,37 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D18" s="15">
+        <v>4</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-25</v>
       </c>
       <c r="F18" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>100</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I18" s="15">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J18" s="15">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K18" s="14">
-        <v>66.666666666666</v>
+        <v>43.75</v>
       </c>
       <c r="L18" s="14">
-        <v>-16.666666666666</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="M18" s="14">
-        <v>42.857142857142</v>
+        <v>35.294117647058</v>
       </c>
       <c r="N18" s="13" t="s">
         <v>21</v>
@@ -1076,37 +1076,37 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E19" s="14">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G19" s="15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H19" s="14">
-        <v>-26.086956521739</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I19" s="15">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J19" s="15">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K19" s="14">
-        <v>-28.571428571428</v>
+        <v>-24.590163934426</v>
       </c>
       <c r="L19" s="14">
-        <v>-29.824561403508</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="M19" s="14">
-        <v>33.333333333333</v>
+        <v>24.324324324324</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>21</v>
@@ -1116,38 +1116,38 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>4</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G20" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
         <v>100</v>
       </c>
       <c r="I20" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J20" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K20" s="14">
-        <v>28.571428571428</v>
+        <v>46.666666666666</v>
       </c>
       <c r="L20" s="14">
-        <v>12.5</v>
+        <v>29.411764705882</v>
       </c>
       <c r="M20" s="14">
-        <v>63.636363636363</v>
+        <v>100</v>
       </c>
       <c r="N20" s="13" t="s">
         <v>21</v>
@@ -1161,34 +1161,34 @@
         <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>-16.666666666666</v>
+        <v>15.384615384615</v>
       </c>
       <c r="F21" s="17">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H21" s="18">
-        <v>23.728813559322</v>
+        <v>14.516129032258</v>
       </c>
       <c r="I21" s="17">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="J21" s="17">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="K21" s="18">
-        <v>17.164179104477</v>
+        <v>17.687074829932</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.848484848484</v>
+        <v>-5.464480874316</v>
       </c>
       <c r="M21" s="18">
-        <v>30.833333333333</v>
+        <v>27.205882352941</v>
       </c>
       <c r="N21" s="19" t="s">
         <v>21</v>
@@ -1211,7 +1211,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="14">
         <v>-100</v>
@@ -1267,7 +1267,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L23" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M23" s="14">
         <v>-33.333333333333</v>
@@ -1281,37 +1281,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" s="15">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E24" s="14">
-        <v>-44.444444444444</v>
+        <v>-20</v>
       </c>
       <c r="F24" s="15">
         <v>52</v>
       </c>
       <c r="G24" s="15">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H24" s="14">
-        <v>-29.729729729729</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I24" s="15">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="J24" s="15">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="K24" s="14">
-        <v>-27.516778523489</v>
+        <v>-27.218934911242</v>
       </c>
       <c r="L24" s="14">
-        <v>-11.475409836065</v>
+        <v>-10.869565217391</v>
       </c>
       <c r="M24" s="14">
-        <v>56.521739130434</v>
+        <v>61.842105263157</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1321,35 +1321,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>1</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E25" s="14">
-        <v>-88.888888888888</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="15">
         <v>3</v>
       </c>
       <c r="G25" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H25" s="14">
-        <v>-85.714285714285</v>
+        <v>-86.363636363636</v>
       </c>
       <c r="I25" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J25" s="15">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K25" s="14">
-        <v>-73.469387755102</v>
+        <v>-74.074074074074</v>
       </c>
       <c r="L25" s="14">
-        <v>-7.142857142857</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1363,37 +1363,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>-22.222222222222</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G26" s="15">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H26" s="14">
-        <v>-23.333333333333</v>
+        <v>3.571428571428</v>
       </c>
       <c r="I26" s="15">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="J26" s="15">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K26" s="14">
-        <v>7.843137254901</v>
+        <v>17.543859649122</v>
       </c>
       <c r="L26" s="14">
-        <v>5.769230769230</v>
+        <v>11.666666666666</v>
       </c>
       <c r="M26" s="14">
-        <v>-20.289855072463</v>
+        <v>-12.987012987013</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1406,11 +1406,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1444,35 +1444,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
         <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K28" s="14">
-        <v>-63.636363636363</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-033pct.xlsx
+++ b/data/source/weekly/cs-en-us-033pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -911,8 +911,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -920,29 +920,29 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="15">
+        <v>1</v>
       </c>
       <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15">
         <v>2</v>
-      </c>
-      <c r="H15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I15" s="15">
-        <v>1</v>
       </c>
       <c r="J15" s="15">
         <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="13" t="s">
         <v>21</v>
@@ -953,37 +953,37 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>-66.666666666666</v>
+        <v>250</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="I16" s="15">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J16" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K16" s="14">
-        <v>41.176470588235</v>
+        <v>63.157894736842</v>
       </c>
       <c r="L16" s="14">
-        <v>-7.692307692307</v>
+        <v>14.814814814814</v>
       </c>
       <c r="M16" s="14">
-        <v>-35.135135135135</v>
+        <v>-24.390243902439</v>
       </c>
       <c r="N16" s="13" t="s">
         <v>21</v>
@@ -996,35 +996,35 @@
       <c r="C17" s="15">
         <v>2</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="D17" s="15">
+        <v>4</v>
+      </c>
+      <c r="E17" s="14">
+        <v>-50</v>
       </c>
       <c r="F17" s="15">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G17" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H17" s="14">
-        <v>26.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J17" s="15">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K17" s="14">
-        <v>67.647058823529</v>
+        <v>57.894736842105</v>
       </c>
       <c r="L17" s="14">
-        <v>16.326530612244</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M17" s="14">
-        <v>83.870967741935</v>
+        <v>81.818181818181</v>
       </c>
       <c r="N17" s="13" t="s">
         <v>21</v>
@@ -1035,37 +1035,37 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
         <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>-25</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G18" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H18" s="14">
-        <v>44.444444444444</v>
+        <v>50</v>
       </c>
       <c r="I18" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J18" s="15">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K18" s="14">
-        <v>43.75</v>
+        <v>30</v>
       </c>
       <c r="L18" s="14">
-        <v>-11.538461538461</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M18" s="14">
-        <v>35.294117647058</v>
+        <v>36.842105263157</v>
       </c>
       <c r="N18" s="13" t="s">
         <v>21</v>
@@ -1079,34 +1079,34 @@
         <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E19" s="14">
-        <v>0</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F19" s="15">
         <v>20</v>
       </c>
       <c r="G19" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H19" s="14">
-        <v>-9.090909090909</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="I19" s="15">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J19" s="15">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="K19" s="14">
-        <v>-24.590163934426</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="L19" s="14">
-        <v>-25.806451612903</v>
+        <v>-24.637681159420</v>
       </c>
       <c r="M19" s="14">
-        <v>24.324324324324</v>
+        <v>15.555555555555</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>21</v>
@@ -1116,38 +1116,38 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>4</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="15">
         <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G20" s="15">
         <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I20" s="15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J20" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20" s="14">
-        <v>46.666666666666</v>
+        <v>31.25</v>
       </c>
       <c r="L20" s="14">
-        <v>29.411764705882</v>
+        <v>5</v>
       </c>
       <c r="M20" s="14">
-        <v>100</v>
+        <v>61.538461538461</v>
       </c>
       <c r="N20" s="13" t="s">
         <v>21</v>
@@ -1158,37 +1158,37 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>15.384615384615</v>
+        <v>-20</v>
       </c>
       <c r="F21" s="17">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G21" s="17">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H21" s="18">
-        <v>14.516129032258</v>
+        <v>10.447761194029</v>
       </c>
       <c r="I21" s="17">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="J21" s="17">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="K21" s="18">
-        <v>17.687074829932</v>
+        <v>14.970059880239</v>
       </c>
       <c r="L21" s="18">
-        <v>-5.464480874316</v>
+        <v>-4.950495049504</v>
       </c>
       <c r="M21" s="18">
-        <v>27.205882352941</v>
+        <v>24.675324675324</v>
       </c>
       <c r="N21" s="19" t="s">
         <v>21</v>
@@ -1210,11 +1210,11 @@
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
-        <v>-100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>20</v>
@@ -1281,37 +1281,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D24" s="15">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E24" s="14">
-        <v>-20</v>
+        <v>46.153846153846</v>
       </c>
       <c r="F24" s="15">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G24" s="15">
         <v>76</v>
       </c>
       <c r="H24" s="14">
-        <v>-31.578947368421</v>
+        <v>-25</v>
       </c>
       <c r="I24" s="15">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="J24" s="15">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="K24" s="14">
-        <v>-27.218934911242</v>
+        <v>-23.626373626373</v>
       </c>
       <c r="L24" s="14">
-        <v>-10.869565217391</v>
+        <v>-11.464968152866</v>
       </c>
       <c r="M24" s="14">
-        <v>61.842105263157</v>
+        <v>52.747252747252</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1321,35 +1321,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="15">
+        <v>2</v>
       </c>
       <c r="D25" s="15">
+        <v>2</v>
+      </c>
+      <c r="E25" s="14">
+        <v>0</v>
+      </c>
+      <c r="F25" s="15">
         <v>5</v>
       </c>
-      <c r="E25" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F25" s="15">
-        <v>3</v>
-      </c>
       <c r="G25" s="15">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H25" s="14">
-        <v>-86.363636363636</v>
+        <v>-73.684210526315</v>
       </c>
       <c r="I25" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J25" s="15">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K25" s="14">
-        <v>-74.074074074074</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L25" s="14">
-        <v>-6.666666666666</v>
+        <v>-36</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1363,37 +1363,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>83.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="15">
         <v>29</v>
       </c>
       <c r="G26" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H26" s="14">
-        <v>3.571428571428</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J26" s="15">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="K26" s="14">
-        <v>17.543859649122</v>
+        <v>7.575757575757</v>
       </c>
       <c r="L26" s="14">
-        <v>11.666666666666</v>
+        <v>7.575757575757</v>
       </c>
       <c r="M26" s="14">
-        <v>-12.987012987013</v>
+        <v>-13.414634146341</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1403,8 +1403,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1412,26 +1412,26 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="15">
+        <v>1</v>
       </c>
       <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="14">
+        <v>0</v>
+      </c>
+      <c r="I27" s="15">
         <v>2</v>
-      </c>
-      <c r="H27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I27" s="15">
-        <v>1</v>
       </c>
       <c r="J27" s="15">
         <v>4</v>
       </c>
       <c r="K27" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1445,34 +1445,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G28" s="15">
         <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="I28" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J28" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K28" s="14">
-        <v>-58.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="L28" s="14">
-        <v>-44.444444444444</v>
+        <v>-10</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-033pct.xlsx
+++ b/data/source/weekly/cs-en-us-033pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -714,7 +714,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -911,8 +911,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -953,37 +953,37 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
         <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F16" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>87.5</v>
+        <v>88.888888888888</v>
       </c>
       <c r="I16" s="15">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J16" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K16" s="14">
-        <v>63.157894736842</v>
+        <v>71.428571428571</v>
       </c>
       <c r="L16" s="14">
-        <v>14.814814814814</v>
+        <v>5.882352941176</v>
       </c>
       <c r="M16" s="14">
-        <v>-24.390243902439</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="N16" s="13" t="s">
         <v>21</v>
@@ -994,37 +994,37 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>-50</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F17" s="15">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G17" s="15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H17" s="14">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="I17" s="15">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J17" s="15">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K17" s="14">
-        <v>57.894736842105</v>
+        <v>47.727272727272</v>
       </c>
       <c r="L17" s="14">
-        <v>9.090909090909</v>
+        <v>10.169491525423</v>
       </c>
       <c r="M17" s="14">
-        <v>81.818181818181</v>
+        <v>58.536585365853</v>
       </c>
       <c r="N17" s="13" t="s">
         <v>21</v>
@@ -1038,34 +1038,34 @@
         <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G18" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>50</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I18" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J18" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" s="14">
-        <v>30</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L18" s="14">
-        <v>-7.142857142857</v>
+        <v>-10</v>
       </c>
       <c r="M18" s="14">
-        <v>36.842105263157</v>
+        <v>17.391304347826</v>
       </c>
       <c r="N18" s="13" t="s">
         <v>21</v>
@@ -1079,34 +1079,34 @@
         <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E19" s="14">
-        <v>-44.444444444444</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" s="15">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H19" s="14">
-        <v>-23.076923076923</v>
+        <v>-12.5</v>
       </c>
       <c r="I19" s="15">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J19" s="15">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K19" s="14">
-        <v>-25.714285714285</v>
+        <v>-21.917808219178</v>
       </c>
       <c r="L19" s="14">
-        <v>-24.637681159420</v>
+        <v>-27.848101265822</v>
       </c>
       <c r="M19" s="14">
-        <v>15.555555555555</v>
+        <v>7.547169811320</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>21</v>
@@ -1116,38 +1116,38 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F20" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G20" s="15">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H20" s="14">
-        <v>20</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I20" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J20" s="15">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K20" s="14">
-        <v>31.25</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L20" s="14">
-        <v>5</v>
+        <v>4.761904761904</v>
       </c>
       <c r="M20" s="14">
-        <v>61.538461538461</v>
+        <v>46.666666666666</v>
       </c>
       <c r="N20" s="13" t="s">
         <v>21</v>
@@ -1161,34 +1161,34 @@
         <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-20</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="G21" s="17">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H21" s="18">
-        <v>10.447761194029</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I21" s="17">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="J21" s="17">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="K21" s="18">
-        <v>14.970059880239</v>
+        <v>12.365591397849</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.950495049504</v>
+        <v>-7.522123893805</v>
       </c>
       <c r="M21" s="18">
-        <v>24.675324675324</v>
+        <v>15.469613259668</v>
       </c>
       <c r="N21" s="19" t="s">
         <v>21</v>
@@ -1239,8 +1239,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>3</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1248,29 +1248,29 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="15">
-        <v>1</v>
-      </c>
-      <c r="H23" s="14">
-        <v>-100</v>
+      <c r="F23" s="15">
+        <v>3</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J23" s="15">
         <v>3</v>
       </c>
       <c r="K23" s="14">
-        <v>-33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L23" s="14">
-        <v>-66.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M23" s="14">
-        <v>-33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1281,37 +1281,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D24" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E24" s="14">
-        <v>46.153846153846</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F24" s="15">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G24" s="15">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H24" s="14">
-        <v>-25</v>
+        <v>-12.676056338028</v>
       </c>
       <c r="I24" s="15">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="J24" s="15">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="K24" s="14">
-        <v>-23.626373626373</v>
+        <v>-21.243523316062</v>
       </c>
       <c r="L24" s="14">
-        <v>-11.464968152866</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="M24" s="14">
-        <v>52.747252747252</v>
+        <v>56.701030927835</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1325,31 +1325,31 @@
         <v>2</v>
       </c>
       <c r="D25" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" s="15">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H25" s="14">
-        <v>-73.684210526315</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="I25" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J25" s="15">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K25" s="14">
-        <v>-71.428571428571</v>
+        <v>-68.421052631578</v>
       </c>
       <c r="L25" s="14">
-        <v>-36</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1366,34 +1366,34 @@
         <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G26" s="15">
         <v>30</v>
       </c>
       <c r="H26" s="14">
-        <v>-3.333333333333</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I26" s="15">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J26" s="15">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K26" s="14">
-        <v>7.575757575757</v>
+        <v>6.944444444444</v>
       </c>
       <c r="L26" s="14">
-        <v>7.575757575757</v>
+        <v>0</v>
       </c>
       <c r="M26" s="14">
-        <v>-13.414634146341</v>
+        <v>-12.5</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1403,8 +1403,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1445,34 +1445,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="15">
         <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K28" s="14">
-        <v>-40</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="L28" s="14">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1516,7 +1516,7 @@
         <v>21</v>
       </c>
       <c r="M29" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="13" t="s">
         <v>21</v>
@@ -1557,7 +1557,7 @@
         <v>21</v>
       </c>
       <c r="M30" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="13" t="s">
         <v>21</v>
@@ -1594,8 +1594,8 @@
       <c r="K31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="14">
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-033pct.xlsx
+++ b/data/source/weekly/cs-en-us-033pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -923,11 +923,11 @@
       <c r="F15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>0</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
@@ -942,7 +942,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="M15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N15" s="13" t="s">
         <v>21</v>
@@ -953,37 +953,37 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="15">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" s="14">
-        <v>88.888888888888</v>
+        <v>40</v>
       </c>
       <c r="I16" s="15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J16" s="15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K16" s="14">
-        <v>71.428571428571</v>
+        <v>54.166666666666</v>
       </c>
       <c r="L16" s="14">
-        <v>5.882352941176</v>
+        <v>-2.631578947368</v>
       </c>
       <c r="M16" s="14">
-        <v>-21.739130434782</v>
+        <v>-26</v>
       </c>
       <c r="N16" s="13" t="s">
         <v>21</v>
@@ -997,34 +997,34 @@
         <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>-16.666666666666</v>
+        <v>25</v>
       </c>
       <c r="F17" s="15">
+        <v>15</v>
+      </c>
+      <c r="G17" s="15">
         <v>14</v>
       </c>
-      <c r="G17" s="15">
-        <v>16</v>
-      </c>
       <c r="H17" s="14">
-        <v>-12.5</v>
+        <v>7.142857142857</v>
       </c>
       <c r="I17" s="15">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J17" s="15">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K17" s="14">
-        <v>47.727272727272</v>
+        <v>45.833333333333</v>
       </c>
       <c r="L17" s="14">
-        <v>10.169491525423</v>
+        <v>12.903225806451</v>
       </c>
       <c r="M17" s="14">
-        <v>58.536585365853</v>
+        <v>59.090909090909</v>
       </c>
       <c r="N17" s="13" t="s">
         <v>21</v>
@@ -1038,34 +1038,34 @@
         <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>-11.111111111111</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I18" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J18" s="15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K18" s="14">
-        <v>28.571428571428</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L18" s="14">
-        <v>-10</v>
+        <v>-12.5</v>
       </c>
       <c r="M18" s="14">
-        <v>17.391304347826</v>
+        <v>21.739130434782</v>
       </c>
       <c r="N18" s="13" t="s">
         <v>21</v>
@@ -1076,37 +1076,37 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" s="14">
-        <v>66.666666666666</v>
+        <v>300</v>
       </c>
       <c r="F19" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G19" s="15">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H19" s="14">
-        <v>-12.5</v>
+        <v>21.052631578947</v>
       </c>
       <c r="I19" s="15">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="J19" s="15">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K19" s="14">
-        <v>-21.917808219178</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L19" s="14">
-        <v>-27.848101265822</v>
+        <v>-22.619047619047</v>
       </c>
       <c r="M19" s="14">
-        <v>7.547169811320</v>
+        <v>16.071428571428</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>21</v>
@@ -1120,34 +1120,34 @@
         <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E20" s="14">
-        <v>-85.714285714285</v>
+        <v>-80</v>
       </c>
       <c r="F20" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G20" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H20" s="14">
-        <v>-63.636363636363</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I20" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J20" s="15">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K20" s="14">
-        <v>-4.347826086956</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L20" s="14">
-        <v>4.761904761904</v>
+        <v>4.347826086956</v>
       </c>
       <c r="M20" s="14">
-        <v>46.666666666666</v>
+        <v>41.176470588235</v>
       </c>
       <c r="N20" s="13" t="s">
         <v>21</v>
@@ -1158,37 +1158,37 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.789473684210</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G21" s="17">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.142857142857</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="I21" s="17">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="J21" s="17">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="K21" s="18">
-        <v>12.365591397849</v>
+        <v>11.330049261083</v>
       </c>
       <c r="L21" s="18">
-        <v>-7.522123893805</v>
+        <v>-6.611570247933</v>
       </c>
       <c r="M21" s="18">
-        <v>15.469613259668</v>
+        <v>16.494845360824</v>
       </c>
       <c r="N21" s="19" t="s">
         <v>21</v>
@@ -1239,35 +1239,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>3</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
         <v>3</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="14">
+        <v>200</v>
       </c>
       <c r="I23" s="15">
         <v>5</v>
       </c>
       <c r="J23" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" s="14">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L23" s="14">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M23" s="14">
         <v>66.666666666666</v>
@@ -1281,37 +1281,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D24" s="15">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E24" s="14">
-        <v>18.181818181818</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F24" s="15">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G24" s="15">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="H24" s="14">
-        <v>-12.676056338028</v>
+        <v>6.779661016949</v>
       </c>
       <c r="I24" s="15">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="J24" s="15">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="K24" s="14">
-        <v>-21.243523316062</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="L24" s="14">
-        <v>-9.523809523809</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M24" s="14">
-        <v>56.701030927835</v>
+        <v>61.538461538461</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1322,34 +1322,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E25" s="14">
-        <v>100</v>
+        <v>-75</v>
       </c>
       <c r="F25" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" s="15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H25" s="14">
-        <v>-64.705882352941</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I25" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J25" s="15">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K25" s="14">
-        <v>-68.421052631578</v>
+        <v>-68.852459016393</v>
       </c>
       <c r="L25" s="14">
-        <v>-35.714285714285</v>
+        <v>-44.117647058823</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1363,37 +1363,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14">
         <v>0</v>
       </c>
       <c r="F26" s="15">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G26" s="15">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H26" s="14">
-        <v>-6.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I26" s="15">
+        <v>82</v>
+      </c>
+      <c r="J26" s="15">
         <v>77</v>
       </c>
-      <c r="J26" s="15">
-        <v>72</v>
-      </c>
       <c r="K26" s="14">
-        <v>6.944444444444</v>
+        <v>6.493506493506</v>
       </c>
       <c r="L26" s="14">
         <v>0</v>
       </c>
       <c r="M26" s="14">
-        <v>-12.5</v>
+        <v>-13.684210526315</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1415,11 +1415,11 @@
       <c r="F27" s="15">
         <v>1</v>
       </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
-      <c r="H27" s="14">
-        <v>0</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="15">
         <v>2</v>
@@ -1444,14 +1444,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-50</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>6</v>
@@ -1472,7 +1472,7 @@
         <v>-41.176470588235</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1626,8 +1626,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="15">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1635,8 +1635,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="15">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1644,8 +1644,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="15">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-033pct.xlsx
+++ b/data/source/weekly/cs-en-us-033pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -714,7 +714,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -911,8 +911,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -921,7 +921,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -930,19 +930,19 @@
         <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="15">
         <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="L15" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N15" s="13" t="s">
         <v>21</v>
@@ -952,38 +952,38 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>2</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G16" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I16" s="15">
         <v>37</v>
       </c>
       <c r="J16" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K16" s="14">
-        <v>54.166666666666</v>
+        <v>48</v>
       </c>
       <c r="L16" s="14">
-        <v>-2.631578947368</v>
+        <v>-13.953488372093</v>
       </c>
       <c r="M16" s="14">
-        <v>-26</v>
+        <v>-31.481481481481</v>
       </c>
       <c r="N16" s="13" t="s">
         <v>21</v>
@@ -994,37 +994,37 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>3</v>
+      </c>
+      <c r="D17" s="15">
         <v>5</v>
       </c>
-      <c r="D17" s="15">
-        <v>4</v>
-      </c>
       <c r="E17" s="14">
-        <v>25</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="15">
         <v>15</v>
       </c>
       <c r="G17" s="15">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H17" s="14">
-        <v>7.142857142857</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I17" s="15">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J17" s="15">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K17" s="14">
-        <v>45.833333333333</v>
+        <v>37.735849056603</v>
       </c>
       <c r="L17" s="14">
-        <v>12.903225806451</v>
+        <v>12.307692307692</v>
       </c>
       <c r="M17" s="14">
-        <v>59.090909090909</v>
+        <v>55.319148936170</v>
       </c>
       <c r="N17" s="13" t="s">
         <v>21</v>
@@ -1035,13 +1035,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
         <v>7</v>
@@ -1053,19 +1053,19 @@
         <v>-41.666666666666</v>
       </c>
       <c r="I18" s="15">
+        <v>32</v>
+      </c>
+      <c r="J18" s="15">
         <v>28</v>
       </c>
-      <c r="J18" s="15">
-        <v>24</v>
-      </c>
       <c r="K18" s="14">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L18" s="14">
-        <v>-12.5</v>
+        <v>-3.030303030303</v>
       </c>
       <c r="M18" s="14">
-        <v>21.739130434782</v>
+        <v>23.076923076923</v>
       </c>
       <c r="N18" s="13" t="s">
         <v>21</v>
@@ -1076,37 +1076,37 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>300</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F19" s="15">
         <v>23</v>
       </c>
       <c r="G19" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H19" s="14">
-        <v>21.052631578947</v>
+        <v>9.523809523809</v>
       </c>
       <c r="I19" s="15">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J19" s="15">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="K19" s="14">
-        <v>-13.333333333333</v>
+        <v>-15.853658536585</v>
       </c>
       <c r="L19" s="14">
-        <v>-22.619047619047</v>
+        <v>-26.595744680851</v>
       </c>
       <c r="M19" s="14">
-        <v>16.071428571428</v>
+        <v>18.965517241379</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>21</v>
@@ -1117,37 +1117,37 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15">
+        <v>2</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="15">
         <v>5</v>
       </c>
-      <c r="E20" s="14">
-        <v>-80</v>
-      </c>
-      <c r="F20" s="15">
-        <v>6</v>
-      </c>
       <c r="G20" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H20" s="14">
-        <v>-57.142857142857</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="I20" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J20" s="15">
         <v>28</v>
       </c>
       <c r="K20" s="14">
-        <v>-14.285714285714</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L20" s="14">
-        <v>4.347826086956</v>
+        <v>4</v>
       </c>
       <c r="M20" s="14">
-        <v>41.176470588235</v>
+        <v>30</v>
       </c>
       <c r="N20" s="13" t="s">
         <v>21</v>
@@ -1158,37 +1158,37 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
         <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="F21" s="17">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.347826086956</v>
+        <v>-12.328767123287</v>
       </c>
       <c r="I21" s="17">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="J21" s="17">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="K21" s="18">
-        <v>11.330049261083</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.611570247933</v>
+        <v>-8.745247148288</v>
       </c>
       <c r="M21" s="18">
-        <v>16.494845360824</v>
+        <v>14.832535885167</v>
       </c>
       <c r="N21" s="19" t="s">
         <v>21</v>
@@ -1239,38 +1239,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="C23" s="15">
         <v>1</v>
       </c>
-      <c r="E23" s="14">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="15">
         <v>1</v>
       </c>
       <c r="H23" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I23" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23" s="15">
         <v>4</v>
       </c>
       <c r="K23" s="14">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L23" s="14">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="M23" s="14">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1281,13 +1281,13 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D24" s="15">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E24" s="14">
-        <v>6.666666666666</v>
+        <v>-10</v>
       </c>
       <c r="F24" s="15">
         <v>63</v>
@@ -1299,19 +1299,19 @@
         <v>6.779661016949</v>
       </c>
       <c r="I24" s="15">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="J24" s="15">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="K24" s="14">
-        <v>-19.230769230769</v>
+        <v>-19.736842105263</v>
       </c>
       <c r="L24" s="14">
-        <v>-11.111111111111</v>
+        <v>-8.955223880597</v>
       </c>
       <c r="M24" s="14">
-        <v>61.538461538461</v>
+        <v>57.758620689655</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1321,35 +1321,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>1</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="14">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="15">
         <v>5</v>
       </c>
       <c r="G25" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H25" s="14">
-        <v>-58.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="15">
         <v>19</v>
       </c>
       <c r="J25" s="15">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K25" s="14">
-        <v>-68.852459016393</v>
+        <v>-70.3125</v>
       </c>
       <c r="L25" s="14">
-        <v>-44.117647058823</v>
+        <v>-48.648648648648</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1363,37 +1363,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F26" s="15">
         <v>26</v>
       </c>
       <c r="G26" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H26" s="14">
-        <v>0</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I26" s="15">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J26" s="15">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K26" s="14">
-        <v>6.493506493506</v>
+        <v>7.058823529411</v>
       </c>
       <c r="L26" s="14">
-        <v>0</v>
+        <v>7.058823529411</v>
       </c>
       <c r="M26" s="14">
-        <v>-13.684210526315</v>
+        <v>-9.900990099009</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1403,8 +1403,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1413,7 +1413,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1422,16 +1422,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="15">
         <v>4</v>
       </c>
       <c r="K27" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="L27" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1444,35 +1444,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="15">
+        <v>2</v>
+      </c>
+      <c r="D28" s="15">
+        <v>2</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="14">
         <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J28" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K28" s="14">
-        <v>-41.176470588235</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="L28" s="14">
-        <v>-9.090909090909</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1626,8 +1626,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="15">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-033pct.xlsx
+++ b/data/source/weekly/cs-en-us-033pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -911,38 +911,38 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="15">
+        <v>2</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
+      <c r="G15" s="15">
         <v>2</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="H15" s="14">
+        <v>-50</v>
       </c>
       <c r="I15" s="15">
         <v>3</v>
       </c>
       <c r="J15" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K15" s="14">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N15" s="13" t="s">
         <v>21</v>
@@ -952,38 +952,38 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>1</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15">
+        <v>39</v>
+      </c>
+      <c r="J16" s="15">
+        <v>26</v>
+      </c>
+      <c r="K16" s="14">
         <v>50</v>
       </c>
-      <c r="I16" s="15">
-        <v>37</v>
-      </c>
-      <c r="J16" s="15">
-        <v>25</v>
-      </c>
-      <c r="K16" s="14">
-        <v>48</v>
-      </c>
       <c r="L16" s="14">
-        <v>-13.953488372093</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M16" s="14">
-        <v>-31.481481481481</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="N16" s="13" t="s">
         <v>21</v>
@@ -997,34 +997,34 @@
         <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" s="14">
-        <v>-40</v>
+        <v>-62.5</v>
       </c>
       <c r="F17" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H17" s="14">
-        <v>-21.052631578947</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="I17" s="15">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J17" s="15">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="K17" s="14">
-        <v>37.735849056603</v>
+        <v>24.590163934426</v>
       </c>
       <c r="L17" s="14">
-        <v>12.307692307692</v>
+        <v>8.571428571428</v>
       </c>
       <c r="M17" s="14">
-        <v>55.319148936170</v>
+        <v>58.333333333333</v>
       </c>
       <c r="N17" s="13" t="s">
         <v>21</v>
@@ -1035,10 +1035,10 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
         <v>0</v>
@@ -1047,25 +1047,25 @@
         <v>7</v>
       </c>
       <c r="G18" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>-41.666666666666</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I18" s="15">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J18" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K18" s="14">
-        <v>14.285714285714</v>
+        <v>13.793103448275</v>
       </c>
       <c r="L18" s="14">
-        <v>-3.030303030303</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M18" s="14">
-        <v>23.076923076923</v>
+        <v>22.222222222222</v>
       </c>
       <c r="N18" s="13" t="s">
         <v>21</v>
@@ -1076,37 +1076,37 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E19" s="14">
-        <v>-28.571428571428</v>
+        <v>250</v>
       </c>
       <c r="F19" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G19" s="15">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H19" s="14">
-        <v>9.523809523809</v>
+        <v>78.571428571428</v>
       </c>
       <c r="I19" s="15">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="J19" s="15">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K19" s="14">
-        <v>-15.853658536585</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="L19" s="14">
-        <v>-26.595744680851</v>
+        <v>-27.619047619047</v>
       </c>
       <c r="M19" s="14">
-        <v>18.965517241379</v>
+        <v>15.151515151515</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>21</v>
@@ -1116,38 +1116,38 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="15">
+        <v>5</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
         <v>5</v>
       </c>
       <c r="G20" s="15">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H20" s="14">
-        <v>-61.538461538461</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="I20" s="15">
         <v>26</v>
       </c>
       <c r="J20" s="15">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K20" s="14">
-        <v>-7.142857142857</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="L20" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M20" s="14">
-        <v>30</v>
+        <v>18.181818181818</v>
       </c>
       <c r="N20" s="13" t="s">
         <v>21</v>
@@ -1158,37 +1158,37 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-11.764705882352</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="F21" s="17">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G21" s="17">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.328767123287</v>
+        <v>-15.277777777777</v>
       </c>
       <c r="I21" s="17">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="J21" s="17">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="K21" s="18">
-        <v>9.090909090909</v>
+        <v>5.857740585774</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.745247148288</v>
+        <v>-11.228070175438</v>
       </c>
       <c r="M21" s="18">
-        <v>14.832535885167</v>
+        <v>12.444444444444</v>
       </c>
       <c r="N21" s="19" t="s">
         <v>21</v>
@@ -1198,8 +1198,8 @@
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1207,8 +1207,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="15">
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1216,20 +1216,20 @@
       <c r="H22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I22" s="13" t="s">
-        <v>20</v>
+      <c r="I22" s="15">
+        <v>1</v>
       </c>
       <c r="J22" s="15">
         <v>3</v>
       </c>
       <c r="K22" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L22" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M22" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1239,38 +1239,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="15">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="14">
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="14">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="I23" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K23" s="14">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L23" s="14">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="M23" s="14">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1281,37 +1281,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D24" s="15">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E24" s="14">
-        <v>-10</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F24" s="15">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G24" s="15">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H24" s="14">
-        <v>6.779661016949</v>
+        <v>-8.620689655172</v>
       </c>
       <c r="I24" s="15">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="J24" s="15">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="K24" s="14">
-        <v>-19.736842105263</v>
+        <v>-20</v>
       </c>
       <c r="L24" s="14">
-        <v>-8.955223880597</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M24" s="14">
-        <v>57.758620689655</v>
+        <v>52.380952380952</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1321,35 +1321,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="15">
+        <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="14">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F25" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G25" s="15">
         <v>10</v>
       </c>
       <c r="H25" s="14">
+        <v>-30</v>
+      </c>
+      <c r="I25" s="15">
+        <v>23</v>
+      </c>
+      <c r="J25" s="15">
+        <v>66</v>
+      </c>
+      <c r="K25" s="14">
+        <v>-65.151515151515</v>
+      </c>
+      <c r="L25" s="14">
         <v>-50</v>
-      </c>
-      <c r="I25" s="15">
-        <v>19</v>
-      </c>
-      <c r="J25" s="15">
-        <v>64</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-70.3125</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-48.648648648648</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1363,37 +1363,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>7</v>
+      </c>
+      <c r="D26" s="15">
         <v>10</v>
       </c>
-      <c r="D26" s="15">
-        <v>8</v>
-      </c>
       <c r="E26" s="14">
-        <v>25</v>
+        <v>-30</v>
       </c>
       <c r="F26" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G26" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H26" s="14">
-        <v>-7.142857142857</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="I26" s="15">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="J26" s="15">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="K26" s="14">
-        <v>7.058823529411</v>
+        <v>4.210526315789</v>
       </c>
       <c r="L26" s="14">
-        <v>7.058823529411</v>
+        <v>8.791208791208</v>
       </c>
       <c r="M26" s="14">
-        <v>-9.900990099009</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1403,32 +1403,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="15">
+        <v>2</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
+      <c r="G27" s="15">
         <v>2</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="H27" s="14">
+        <v>-50</v>
       </c>
       <c r="I27" s="15">
         <v>3</v>
       </c>
       <c r="J27" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K27" s="14">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="14">
         <v>-25</v>
@@ -1445,34 +1445,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="15">
         <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J28" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K28" s="14">
-        <v>-36.842105263157</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="L28" s="14">
-        <v>9.090909090909</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-033pct.xlsx
+++ b/data/source/weekly/cs-en-us-033pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -332,8 +332,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="13">
@@ -556,7 +556,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -583,7 +583,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -873,34 +873,34 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" s="14">
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>-100</v>
+      </c>
+      <c r="L14" s="15">
+        <v>-100</v>
+      </c>
+      <c r="M14" s="15">
         <v>-100</v>
       </c>
       <c r="N14" s="13" t="s">
@@ -914,35 +914,35 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
         <v>2</v>
       </c>
-      <c r="E15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="15">
-        <v>2</v>
-      </c>
-      <c r="H15" s="14">
+      <c r="H15" s="15">
         <v>-50</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="14">
         <v>3</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="14">
         <v>6</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="15">
         <v>-50</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="15">
         <v>0</v>
       </c>
-      <c r="M15" s="14">
-        <v>0</v>
+      <c r="M15" s="15">
+        <v>-25</v>
       </c>
       <c r="N15" s="13" t="s">
         <v>21</v>
@@ -952,38 +952,38 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>0</v>
-      </c>
-      <c r="F16" s="15">
-        <v>7</v>
-      </c>
-      <c r="G16" s="15">
-        <v>7</v>
-      </c>
-      <c r="H16" s="14">
-        <v>0</v>
-      </c>
-      <c r="I16" s="15">
-        <v>39</v>
-      </c>
-      <c r="J16" s="15">
-        <v>26</v>
-      </c>
-      <c r="K16" s="14">
-        <v>50</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-13.333333333333</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-31.578947368421</v>
+      <c r="D16" s="14">
+        <v>5</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-80</v>
+      </c>
+      <c r="F16" s="14">
+        <v>4</v>
+      </c>
+      <c r="G16" s="14">
+        <v>10</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-60</v>
+      </c>
+      <c r="I16" s="14">
+        <v>40</v>
+      </c>
+      <c r="J16" s="14">
+        <v>31</v>
+      </c>
+      <c r="K16" s="15">
+        <v>29.032258064516</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-20</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-32.203389830508</v>
       </c>
       <c r="N16" s="13" t="s">
         <v>21</v>
@@ -993,38 +993,38 @@
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>3</v>
-      </c>
-      <c r="D17" s="15">
-        <v>8</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-62.5</v>
-      </c>
-      <c r="F17" s="15">
-        <v>16</v>
-      </c>
-      <c r="G17" s="15">
-        <v>23</v>
-      </c>
-      <c r="H17" s="14">
-        <v>-30.434782608695</v>
-      </c>
-      <c r="I17" s="15">
-        <v>76</v>
-      </c>
-      <c r="J17" s="15">
-        <v>61</v>
-      </c>
-      <c r="K17" s="14">
-        <v>24.590163934426</v>
-      </c>
-      <c r="L17" s="14">
-        <v>8.571428571428</v>
-      </c>
-      <c r="M17" s="14">
-        <v>58.333333333333</v>
+      <c r="C17" s="14">
+        <v>4</v>
+      </c>
+      <c r="D17" s="14">
+        <v>2</v>
+      </c>
+      <c r="E17" s="15">
+        <v>100</v>
+      </c>
+      <c r="F17" s="14">
+        <v>17</v>
+      </c>
+      <c r="G17" s="14">
+        <v>19</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-10.526315789473</v>
+      </c>
+      <c r="I17" s="14">
+        <v>82</v>
+      </c>
+      <c r="J17" s="14">
+        <v>63</v>
+      </c>
+      <c r="K17" s="15">
+        <v>30.158730158730</v>
+      </c>
+      <c r="L17" s="15">
+        <v>10.810810810810</v>
+      </c>
+      <c r="M17" s="15">
+        <v>64</v>
       </c>
       <c r="N17" s="13" t="s">
         <v>21</v>
@@ -1034,38 +1034,38 @@
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
+      <c r="E18" s="15">
+        <v>200</v>
+      </c>
+      <c r="F18" s="14">
+        <v>9</v>
+      </c>
+      <c r="G18" s="14">
+        <v>9</v>
+      </c>
+      <c r="H18" s="15">
         <v>0</v>
       </c>
-      <c r="F18" s="15">
-        <v>7</v>
-      </c>
-      <c r="G18" s="15">
-        <v>9</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-22.222222222222</v>
-      </c>
-      <c r="I18" s="15">
-        <v>33</v>
-      </c>
-      <c r="J18" s="15">
-        <v>29</v>
-      </c>
-      <c r="K18" s="14">
-        <v>13.793103448275</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-8.333333333333</v>
-      </c>
-      <c r="M18" s="14">
-        <v>22.222222222222</v>
+      <c r="I18" s="14">
+        <v>36</v>
+      </c>
+      <c r="J18" s="14">
+        <v>30</v>
+      </c>
+      <c r="K18" s="15">
+        <v>20</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-2.702702702702</v>
+      </c>
+      <c r="M18" s="15">
+        <v>28.571428571428</v>
       </c>
       <c r="N18" s="13" t="s">
         <v>21</v>
@@ -1075,38 +1075,38 @@
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>7</v>
-      </c>
-      <c r="D19" s="15">
-        <v>2</v>
-      </c>
-      <c r="E19" s="14">
-        <v>250</v>
-      </c>
-      <c r="F19" s="15">
-        <v>25</v>
-      </c>
-      <c r="G19" s="15">
-        <v>14</v>
-      </c>
-      <c r="H19" s="14">
-        <v>78.571428571428</v>
-      </c>
-      <c r="I19" s="15">
-        <v>76</v>
-      </c>
-      <c r="J19" s="15">
-        <v>84</v>
-      </c>
-      <c r="K19" s="14">
-        <v>-9.523809523809</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-27.619047619047</v>
-      </c>
-      <c r="M19" s="14">
-        <v>15.151515151515</v>
+      <c r="C19" s="14">
+        <v>6</v>
+      </c>
+      <c r="D19" s="14">
+        <v>8</v>
+      </c>
+      <c r="E19" s="15">
+        <v>-25</v>
+      </c>
+      <c r="F19" s="14">
+        <v>26</v>
+      </c>
+      <c r="G19" s="14">
+        <v>19</v>
+      </c>
+      <c r="H19" s="15">
+        <v>36.842105263157</v>
+      </c>
+      <c r="I19" s="14">
+        <v>82</v>
+      </c>
+      <c r="J19" s="14">
+        <v>92</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-10.869565217391</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-28.070175438596</v>
+      </c>
+      <c r="M19" s="15">
+        <v>10.810810810810</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>21</v>
@@ -1116,38 +1116,38 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="15">
+      <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
+        <v>6</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F20" s="14">
         <v>5</v>
       </c>
-      <c r="E20" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F20" s="15">
-        <v>5</v>
-      </c>
-      <c r="G20" s="15">
-        <v>17</v>
-      </c>
-      <c r="H20" s="14">
-        <v>-70.588235294117</v>
-      </c>
-      <c r="I20" s="15">
-        <v>26</v>
-      </c>
-      <c r="J20" s="15">
-        <v>33</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-21.212121212121</v>
-      </c>
-      <c r="L20" s="14">
-        <v>0</v>
-      </c>
-      <c r="M20" s="14">
-        <v>18.181818181818</v>
+      <c r="G20" s="14">
+        <v>16</v>
+      </c>
+      <c r="H20" s="15">
+        <v>-68.75</v>
+      </c>
+      <c r="I20" s="14">
+        <v>28</v>
+      </c>
+      <c r="J20" s="14">
+        <v>39</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-28.205128205128</v>
+      </c>
+      <c r="L20" s="15">
+        <v>3.703703703703</v>
+      </c>
+      <c r="M20" s="15">
+        <v>21.739130434782</v>
       </c>
       <c r="N20" s="13" t="s">
         <v>21</v>
@@ -1158,37 +1158,37 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>-36.842105263157</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="F21" s="17">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G21" s="17">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.277777777777</v>
+        <v>-18.421052631578</v>
       </c>
       <c r="I21" s="17">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="J21" s="17">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="K21" s="18">
-        <v>5.857740585774</v>
+        <v>3.435114503816</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.228070175438</v>
+        <v>-11.437908496732</v>
       </c>
       <c r="M21" s="18">
-        <v>12.444444444444</v>
+        <v>12.916666666666</v>
       </c>
       <c r="N21" s="19" t="s">
         <v>21</v>
@@ -1198,37 +1198,37 @@
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15">
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="15">
-        <v>1</v>
-      </c>
-      <c r="J22" s="15">
+      <c r="J22" s="14">
         <v>3</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="L22" s="14">
+      <c r="L22" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="M22" s="14">
+      <c r="M22" s="15">
         <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
@@ -1242,34 +1242,34 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
         <v>1</v>
       </c>
-      <c r="E23" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="15">
+      <c r="G23" s="14">
+        <v>2</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I23" s="14">
+        <v>7</v>
+      </c>
+      <c r="J23" s="14">
         <v>5</v>
       </c>
-      <c r="G23" s="15">
-        <v>2</v>
-      </c>
-      <c r="H23" s="14">
-        <v>150</v>
-      </c>
-      <c r="I23" s="15">
-        <v>7</v>
-      </c>
-      <c r="J23" s="15">
-        <v>5</v>
-      </c>
-      <c r="K23" s="14">
+      <c r="K23" s="15">
         <v>40</v>
       </c>
-      <c r="L23" s="14">
+      <c r="L23" s="15">
         <v>-12.5</v>
       </c>
-      <c r="M23" s="14">
+      <c r="M23" s="15">
         <v>75</v>
       </c>
       <c r="N23" s="13" t="s">
@@ -1280,38 +1280,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>11</v>
-      </c>
-      <c r="D24" s="15">
-        <v>12</v>
-      </c>
-      <c r="E24" s="14">
-        <v>-8.333333333333</v>
-      </c>
-      <c r="F24" s="15">
-        <v>53</v>
-      </c>
-      <c r="G24" s="15">
-        <v>58</v>
-      </c>
-      <c r="H24" s="14">
-        <v>-8.620689655172</v>
-      </c>
-      <c r="I24" s="15">
-        <v>192</v>
-      </c>
-      <c r="J24" s="15">
-        <v>240</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-20</v>
-      </c>
-      <c r="L24" s="14">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="M24" s="14">
-        <v>52.380952380952</v>
+      <c r="C24" s="14">
+        <v>13</v>
+      </c>
+      <c r="D24" s="14">
+        <v>7</v>
+      </c>
+      <c r="E24" s="15">
+        <v>85.714285714285</v>
+      </c>
+      <c r="F24" s="14">
+        <v>54</v>
+      </c>
+      <c r="G24" s="14">
+        <v>54</v>
+      </c>
+      <c r="H24" s="15">
+        <v>0</v>
+      </c>
+      <c r="I24" s="14">
+        <v>205</v>
+      </c>
+      <c r="J24" s="14">
+        <v>247</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-17.004048582996</v>
+      </c>
+      <c r="L24" s="15">
+        <v>-18</v>
+      </c>
+      <c r="M24" s="15">
+        <v>45.390070921985</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1321,35 +1321,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>3</v>
-      </c>
-      <c r="D25" s="15">
-        <v>2</v>
-      </c>
-      <c r="E25" s="14">
-        <v>50</v>
-      </c>
-      <c r="F25" s="15">
-        <v>7</v>
-      </c>
-      <c r="G25" s="15">
+      <c r="C25" s="14">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14">
+        <v>1</v>
+      </c>
+      <c r="E25" s="15">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
+        <v>6</v>
+      </c>
+      <c r="G25" s="14">
         <v>10</v>
       </c>
-      <c r="H25" s="14">
-        <v>-30</v>
-      </c>
-      <c r="I25" s="15">
-        <v>23</v>
-      </c>
-      <c r="J25" s="15">
-        <v>66</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-65.151515151515</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-50</v>
+      <c r="H25" s="15">
+        <v>-40</v>
+      </c>
+      <c r="I25" s="14">
+        <v>24</v>
+      </c>
+      <c r="J25" s="14">
+        <v>67</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-64.179104477611</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-54.716981132075</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1362,38 +1362,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>7</v>
-      </c>
-      <c r="D26" s="15">
+      <c r="C26" s="14">
         <v>10</v>
       </c>
-      <c r="E26" s="14">
-        <v>-30</v>
-      </c>
-      <c r="F26" s="15">
-        <v>28</v>
-      </c>
-      <c r="G26" s="15">
-        <v>29</v>
-      </c>
-      <c r="H26" s="14">
-        <v>-3.448275862068</v>
-      </c>
-      <c r="I26" s="15">
-        <v>99</v>
-      </c>
-      <c r="J26" s="15">
-        <v>95</v>
-      </c>
-      <c r="K26" s="14">
-        <v>4.210526315789</v>
-      </c>
-      <c r="L26" s="14">
-        <v>8.791208791208</v>
-      </c>
-      <c r="M26" s="14">
-        <v>-13.157894736842</v>
+      <c r="D26" s="14">
+        <v>12</v>
+      </c>
+      <c r="E26" s="15">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="F26" s="14">
+        <v>32</v>
+      </c>
+      <c r="G26" s="14">
+        <v>35</v>
+      </c>
+      <c r="H26" s="15">
+        <v>-8.571428571428</v>
+      </c>
+      <c r="I26" s="14">
+        <v>108</v>
+      </c>
+      <c r="J26" s="14">
+        <v>107</v>
+      </c>
+      <c r="K26" s="15">
+        <v>0.934579439252</v>
+      </c>
+      <c r="L26" s="15">
+        <v>11.340206185567</v>
+      </c>
+      <c r="M26" s="15">
+        <v>-9.243697478991</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1406,31 +1406,31 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>1</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="15">
-        <v>1</v>
-      </c>
-      <c r="G27" s="15">
-        <v>2</v>
-      </c>
-      <c r="H27" s="14">
+      <c r="H27" s="15">
         <v>-50</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="14">
         <v>3</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="14">
         <v>6</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="15">
         <v>-50</v>
       </c>
-      <c r="L27" s="14">
+      <c r="L27" s="15">
         <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
@@ -1444,35 +1444,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
         <v>2</v>
       </c>
-      <c r="E28" s="14">
+      <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="15">
         <v>-50</v>
       </c>
-      <c r="F28" s="15">
-        <v>4</v>
-      </c>
-      <c r="G28" s="15">
-        <v>6</v>
-      </c>
-      <c r="H28" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="I28" s="15">
-        <v>13</v>
-      </c>
-      <c r="J28" s="15">
-        <v>21</v>
-      </c>
-      <c r="K28" s="14">
-        <v>-38.095238095238</v>
-      </c>
-      <c r="L28" s="14">
-        <v>8.333333333333</v>
+      <c r="I28" s="14">
+        <v>12</v>
+      </c>
+      <c r="J28" s="14">
+        <v>21</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="L28" s="15">
+        <v>-7.692307692307</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1503,7 +1503,7 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I29" s="14">
         <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
@@ -1515,7 +1515,7 @@
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M29" s="14">
+      <c r="M29" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="N29" s="13" t="s">
@@ -1544,7 +1544,7 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="14">
         <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
@@ -1556,7 +1556,7 @@
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M30" s="14">
+      <c r="M30" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="N30" s="13" t="s">
@@ -1585,7 +1585,7 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="14">
         <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
@@ -1594,7 +1594,7 @@
       <c r="K31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="14">
+      <c r="L31" s="15">
         <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
@@ -1635,7 +1635,7 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="15">
+      <c r="F33" s="14">
         <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
@@ -1644,7 +1644,7 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I33" s="14">
         <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
@@ -1761,22 +1761,22 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>0</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>6</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>8</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>1</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>-87.5</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>-83.333333333333</v>
       </c>
       <c r="M39" s="13" t="s">
@@ -1790,25 +1790,25 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>16</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>35</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>19</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>17</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>-10.526315789473</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>-51.428571428571</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>6.25</v>
       </c>
       <c r="N40" s="13" t="s">
@@ -1819,25 +1819,25 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>142</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>327</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>273</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>154</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-43.589743589743</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-52.905198776758</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>8.450704225352</v>
       </c>
       <c r="N41" s="13" t="s">
@@ -1848,25 +1848,25 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>155</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>379</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>315</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>261</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>-17.142857142857</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>-31.134564643799</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>68.387096774193</v>
       </c>
       <c r="N42" s="13" t="s">
@@ -1877,25 +1877,25 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>186</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>366</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>199</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>102</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-48.743718592964</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-72.131147540983</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-45.161290322580</v>
       </c>
       <c r="N43" s="13" t="s">
@@ -1906,25 +1906,25 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>99</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>269</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>199</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>368</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>84.924623115577</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>36.802973977695</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>271.717171717172</v>
       </c>
       <c r="N44" s="13" t="s">
@@ -1935,25 +1935,25 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>133</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>283</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>194</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>134</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-30.927835051546</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-52.650176678445</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>0.751879699248</v>
       </c>
       <c r="N45" s="13" t="s">

--- a/data/source/weekly/cs-en-us-033pct.xlsx
+++ b/data/source/weekly/cs-en-us-033pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -873,11 +873,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="N15" s="13" t="s">
         <v>21</v>
@@ -953,37 +953,37 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="14">
-        <v>5</v>
-      </c>
       <c r="E16" s="15">
-        <v>-80</v>
+        <v>200</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-60</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J16" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>29.032258064516</v>
+        <v>37.5</v>
       </c>
       <c r="L16" s="15">
-        <v>-20</v>
+        <v>-16.981132075471</v>
       </c>
       <c r="M16" s="15">
-        <v>-32.203389830508</v>
+        <v>-32.307692307692</v>
       </c>
       <c r="N16" s="13" t="s">
         <v>21</v>
@@ -994,37 +994,37 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>-60</v>
       </c>
       <c r="F17" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G17" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>-10.526315789473</v>
+        <v>-35</v>
       </c>
       <c r="I17" s="14">
         <v>82</v>
       </c>
       <c r="J17" s="14">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K17" s="15">
-        <v>30.158730158730</v>
+        <v>20.588235294117</v>
       </c>
       <c r="L17" s="15">
-        <v>10.810810810810</v>
+        <v>5.128205128205</v>
       </c>
       <c r="M17" s="15">
-        <v>64</v>
+        <v>54.716981132075</v>
       </c>
       <c r="N17" s="13" t="s">
         <v>21</v>
@@ -1035,37 +1035,37 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>85.714285714285</v>
       </c>
       <c r="I18" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J18" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K18" s="15">
-        <v>20</v>
+        <v>32.258064516129</v>
       </c>
       <c r="L18" s="15">
-        <v>-2.702702702702</v>
+        <v>2.5</v>
       </c>
       <c r="M18" s="15">
-        <v>28.571428571428</v>
+        <v>32.258064516129</v>
       </c>
       <c r="N18" s="13" t="s">
         <v>21</v>
@@ -1076,37 +1076,37 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>5</v>
+      </c>
+      <c r="D19" s="14">
         <v>6</v>
       </c>
-      <c r="D19" s="14">
-        <v>8</v>
-      </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G19" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H19" s="15">
-        <v>36.842105263157</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J19" s="14">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K19" s="15">
-        <v>-10.869565217391</v>
+        <v>-11.224489795918</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.070175438596</v>
+        <v>-28.688524590163</v>
       </c>
       <c r="M19" s="15">
-        <v>10.810810810810</v>
+        <v>8.75</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>21</v>
@@ -1117,37 +1117,37 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H20" s="15">
-        <v>-68.75</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I20" s="14">
         <v>28</v>
       </c>
       <c r="J20" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K20" s="15">
-        <v>-28.205128205128</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>3.703703703703</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="M20" s="15">
-        <v>21.739130434782</v>
+        <v>12</v>
       </c>
       <c r="N20" s="13" t="s">
         <v>21</v>
@@ -1158,37 +1158,37 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>15</v>
+      </c>
+      <c r="D21" s="17">
         <v>16</v>
       </c>
-      <c r="D21" s="17">
-        <v>23</v>
-      </c>
       <c r="E21" s="18">
-        <v>-30.434782608695</v>
+        <v>-6.25</v>
       </c>
       <c r="F21" s="17">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G21" s="17">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.421052631578</v>
+        <v>-20</v>
       </c>
       <c r="I21" s="17">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="J21" s="17">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="K21" s="18">
-        <v>3.435114503816</v>
+        <v>2.517985611510</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.437908496732</v>
+        <v>-12.576687116564</v>
       </c>
       <c r="M21" s="18">
-        <v>12.916666666666</v>
+        <v>9.195402298850</v>
       </c>
       <c r="N21" s="19" t="s">
         <v>21</v>
@@ -1242,11 +1242,11 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>1</v>
@@ -1258,19 +1258,19 @@
         <v>-50</v>
       </c>
       <c r="I23" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K23" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-12.5</v>
+        <v>-25</v>
       </c>
       <c r="M23" s="15">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1281,37 +1281,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E24" s="15">
-        <v>85.714285714285</v>
+        <v>50</v>
       </c>
       <c r="F24" s="14">
         <v>54</v>
       </c>
       <c r="G24" s="14">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>10.204081632653</v>
       </c>
       <c r="I24" s="14">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="J24" s="14">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="K24" s="15">
-        <v>-17.004048582996</v>
+        <v>-15.175097276264</v>
       </c>
       <c r="L24" s="15">
-        <v>-18</v>
+        <v>-21.582733812949</v>
       </c>
       <c r="M24" s="15">
-        <v>45.390070921985</v>
+        <v>46.308724832214</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1321,35 +1321,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>1</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H25" s="15">
-        <v>-40</v>
+        <v>-37.5</v>
       </c>
       <c r="I25" s="14">
         <v>24</v>
       </c>
       <c r="J25" s="14">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K25" s="15">
+        <v>-65.217391304347</v>
+      </c>
+      <c r="L25" s="15">
         <v>-64.179104477611</v>
-      </c>
-      <c r="L25" s="15">
-        <v>-54.716981132075</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1363,37 +1363,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
         <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G26" s="14">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.571428571428</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I26" s="14">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="J26" s="14">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="K26" s="15">
-        <v>0.934579439252</v>
+        <v>-1.680672268907</v>
       </c>
       <c r="L26" s="15">
-        <v>11.340206185567</v>
+        <v>9.345794392523</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.243697478991</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1431,7 +1431,7 @@
         <v>-50</v>
       </c>
       <c r="L27" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1444,35 +1444,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>-42.857142857142</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="L28" s="15">
-        <v>-7.692307692307</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1567,8 +1567,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1576,8 +1576,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1586,7 +1586,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1595,7 +1595,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1635,8 +1635,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-033pct.xlsx
+++ b/data/source/weekly/cs-en-us-033pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -920,14 +920,14 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>3</v>
@@ -953,37 +953,37 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-25</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I16" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J16" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K16" s="15">
-        <v>37.5</v>
+        <v>27.777777777777</v>
       </c>
       <c r="L16" s="15">
-        <v>-16.981132075471</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="M16" s="15">
-        <v>-32.307692307692</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N16" s="13" t="s">
         <v>21</v>
@@ -994,37 +994,37 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H17" s="15">
-        <v>-35</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I17" s="14">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J17" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K17" s="15">
-        <v>20.588235294117</v>
+        <v>22.972972972973</v>
       </c>
       <c r="L17" s="15">
-        <v>5.128205128205</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>54.716981132075</v>
+        <v>56.896551724137</v>
       </c>
       <c r="N17" s="13" t="s">
         <v>21</v>
@@ -1035,37 +1035,37 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>85.714285714285</v>
+        <v>150</v>
       </c>
       <c r="I18" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J18" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K18" s="15">
-        <v>32.258064516129</v>
+        <v>37.5</v>
       </c>
       <c r="L18" s="15">
-        <v>2.5</v>
+        <v>2.325581395348</v>
       </c>
       <c r="M18" s="15">
-        <v>32.258064516129</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N18" s="13" t="s">
         <v>21</v>
@@ -1076,37 +1076,37 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-16.666666666666</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F19" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="I19" s="14">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="J19" s="14">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.224489795918</v>
+        <v>-15.315315315315</v>
       </c>
       <c r="L19" s="15">
-        <v>-28.688524590163</v>
+        <v>-27.131782945736</v>
       </c>
       <c r="M19" s="15">
-        <v>8.75</v>
+        <v>13.253012048192</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>21</v>
@@ -1116,38 +1116,38 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>3</v>
-      </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>-71.428571428571</v>
+        <v>-86.666666666666</v>
       </c>
       <c r="I20" s="14">
         <v>28</v>
       </c>
       <c r="J20" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K20" s="15">
-        <v>-33.333333333333</v>
+        <v>-34.883720930232</v>
       </c>
       <c r="L20" s="15">
         <v>-3.448275862068</v>
       </c>
       <c r="M20" s="15">
-        <v>12</v>
+        <v>7.692307692307</v>
       </c>
       <c r="N20" s="13" t="s">
         <v>21</v>
@@ -1158,37 +1158,37 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>-6.25</v>
+        <v>-24</v>
       </c>
       <c r="F21" s="17">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G21" s="17">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H21" s="18">
-        <v>-20</v>
+        <v>-25.301204819277</v>
       </c>
       <c r="I21" s="17">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="J21" s="17">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="K21" s="18">
-        <v>2.517985611510</v>
+        <v>0.990099009900</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.576687116564</v>
+        <v>-11.815561959654</v>
       </c>
       <c r="M21" s="18">
-        <v>9.195402298850</v>
+        <v>10.869565217391</v>
       </c>
       <c r="N21" s="19" t="s">
         <v>21</v>
@@ -1198,38 +1198,38 @@
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>3</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>200</v>
       </c>
       <c r="F22" s="14">
+        <v>4</v>
+      </c>
+      <c r="G22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="H22" s="15">
+        <v>300</v>
       </c>
       <c r="I22" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1248,26 +1248,26 @@
       <c r="E23" s="15">
         <v>-100</v>
       </c>
-      <c r="F23" s="14">
-        <v>1</v>
+      <c r="F23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I23" s="14">
         <v>6</v>
       </c>
       <c r="J23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L23" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M23" s="15">
         <v>20</v>
@@ -1281,37 +1281,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>50</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F24" s="14">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G24" s="14">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H24" s="15">
-        <v>10.204081632653</v>
+        <v>8.510638297872</v>
       </c>
       <c r="I24" s="14">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="J24" s="14">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.175097276264</v>
+        <v>-16.363636363636</v>
       </c>
       <c r="L24" s="15">
-        <v>-21.582733812949</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M24" s="15">
-        <v>46.308724832214</v>
+        <v>44.654088050314</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1321,35 +1321,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="14">
+        <v>2</v>
       </c>
       <c r="D25" s="14">
         <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H25" s="15">
-        <v>-37.5</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I25" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J25" s="14">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K25" s="15">
-        <v>-65.217391304347</v>
+        <v>-64.788732394366</v>
       </c>
       <c r="L25" s="15">
-        <v>-64.179104477611</v>
+        <v>-63.768115942029</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1363,37 +1363,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>-10</v>
       </c>
       <c r="F26" s="14">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G26" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H26" s="15">
-        <v>-19.047619047619</v>
+        <v>-25</v>
       </c>
       <c r="I26" s="14">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="J26" s="14">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.680672268907</v>
+        <v>-3.100775193798</v>
       </c>
       <c r="L26" s="15">
-        <v>9.345794392523</v>
+        <v>12.612612612612</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.302325581395</v>
+        <v>-11.347517730496</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1412,14 +1412,14 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>3</v>
@@ -1444,23 +1444,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
+        <v>2</v>
+      </c>
+      <c r="G28" s="14">
         <v>3</v>
       </c>
-      <c r="G28" s="14">
-        <v>5</v>
-      </c>
       <c r="H28" s="15">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
         <v>13</v>
@@ -1472,7 +1472,7 @@
         <v>-40.909090909090</v>
       </c>
       <c r="L28" s="15">
-        <v>-13.333333333333</v>
+        <v>-18.75</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1516,7 +1516,7 @@
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="N29" s="13" t="s">
         <v>21</v>
@@ -1557,7 +1557,7 @@
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="13" t="s">
         <v>21</v>
@@ -1567,8 +1567,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-033pct.xlsx
+++ b/data/source/weekly/cs-en-us-033pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -923,11 +923,11 @@
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-100</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>3</v>
@@ -939,10 +939,10 @@
         <v>-50</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="M15" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="N15" s="13" t="s">
         <v>21</v>
@@ -956,10 +956,10 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
         <v>8</v>
@@ -971,19 +971,19 @@
         <v>-27.272727272727</v>
       </c>
       <c r="I16" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J16" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K16" s="15">
-        <v>27.777777777777</v>
+        <v>29.729729729729</v>
       </c>
       <c r="L16" s="15">
-        <v>-20.689655172413</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="M16" s="15">
-        <v>-33.333333333333</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="N16" s="13" t="s">
         <v>21</v>
@@ -994,37 +994,37 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>33.333333333333</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F17" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G17" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>-19.047619047619</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J17" s="14">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="K17" s="15">
-        <v>22.972972972973</v>
+        <v>10.588235294117</v>
       </c>
       <c r="L17" s="15">
-        <v>8.333333333333</v>
+        <v>6.818181818181</v>
       </c>
       <c r="M17" s="15">
-        <v>56.896551724137</v>
+        <v>51.612903225806</v>
       </c>
       <c r="N17" s="13" t="s">
         <v>21</v>
@@ -1038,34 +1038,34 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I18" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J18" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K18" s="15">
-        <v>37.5</v>
+        <v>35.294117647058</v>
       </c>
       <c r="L18" s="15">
-        <v>2.325581395348</v>
+        <v>6.976744186046</v>
       </c>
       <c r="M18" s="15">
-        <v>33.333333333333</v>
+        <v>27.777777777777</v>
       </c>
       <c r="N18" s="13" t="s">
         <v>21</v>
@@ -1076,37 +1076,37 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-46.153846153846</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G19" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.793103448275</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I19" s="14">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J19" s="14">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="K19" s="15">
-        <v>-15.315315315315</v>
+        <v>-14.529914529914</v>
       </c>
       <c r="L19" s="15">
-        <v>-27.131782945736</v>
+        <v>-24.812030075188</v>
       </c>
       <c r="M19" s="15">
-        <v>13.253012048192</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N19" s="13" t="s">
         <v>21</v>
@@ -1116,38 +1116,38 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>-86.666666666666</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="I20" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J20" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K20" s="15">
-        <v>-34.883720930232</v>
+        <v>-32.608695652173</v>
       </c>
       <c r="L20" s="15">
-        <v>-3.448275862068</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="M20" s="15">
-        <v>7.692307692307</v>
+        <v>14.814814814814</v>
       </c>
       <c r="N20" s="13" t="s">
         <v>21</v>
@@ -1158,37 +1158,37 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>-24</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="F21" s="17">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G21" s="17">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.301204819277</v>
+        <v>-26.436781609195</v>
       </c>
       <c r="I21" s="17">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="J21" s="17">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="K21" s="18">
-        <v>0.990099009900</v>
+        <v>-1.226993865030</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.815561959654</v>
+        <v>-12.021857923497</v>
       </c>
       <c r="M21" s="18">
-        <v>10.869565217391</v>
+        <v>6.976744186046</v>
       </c>
       <c r="N21" s="19" t="s">
         <v>21</v>
@@ -1198,23 +1198,23 @@
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>3</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>200</v>
-      </c>
-      <c r="F22" s="14">
-        <v>4</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I22" s="14">
         <v>4</v>
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1242,17 +1242,17 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
         <v>-100</v>
@@ -1281,37 +1281,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>15</v>
+      </c>
+      <c r="D24" s="14">
         <v>14</v>
       </c>
-      <c r="D24" s="14">
-        <v>18</v>
-      </c>
       <c r="E24" s="15">
-        <v>-22.222222222222</v>
+        <v>7.142857142857</v>
       </c>
       <c r="F24" s="14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G24" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H24" s="15">
-        <v>8.510638297872</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I24" s="14">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="J24" s="14">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.363636363636</v>
+        <v>-15.224913494809</v>
       </c>
       <c r="L24" s="15">
-        <v>-23.076923076923</v>
+        <v>-21.974522292993</v>
       </c>
       <c r="M24" s="15">
-        <v>44.654088050314</v>
+        <v>40.804597701149</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1321,35 +1321,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>2</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G25" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H25" s="15">
-        <v>-14.285714285714</v>
+        <v>-62.5</v>
       </c>
       <c r="I25" s="14">
         <v>25</v>
       </c>
       <c r="J25" s="14">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K25" s="15">
-        <v>-64.788732394366</v>
+        <v>-66.216216216216</v>
       </c>
       <c r="L25" s="15">
-        <v>-63.768115942029</v>
+        <v>-66.216216216216</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1363,37 +1363,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>10</v>
+      </c>
+      <c r="D26" s="14">
         <v>9</v>
       </c>
-      <c r="D26" s="14">
-        <v>10</v>
-      </c>
       <c r="E26" s="15">
-        <v>-10</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F26" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G26" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>-25</v>
+        <v>-13.953488372093</v>
       </c>
       <c r="I26" s="14">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J26" s="14">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.100775193798</v>
+        <v>-1.449275362318</v>
       </c>
       <c r="L26" s="15">
-        <v>12.612612612612</v>
+        <v>16.239316239316</v>
       </c>
       <c r="M26" s="15">
-        <v>-11.347517730496</v>
+        <v>-6.206896551724</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1406,17 +1406,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
         <v>-100</v>
@@ -1425,13 +1425,13 @@
         <v>3</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L27" s="15">
-        <v>-40</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1444,8 +1444,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1457,22 +1457,22 @@
         <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
         <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>-40.909090909090</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L28" s="15">
-        <v>-18.75</v>
+        <v>-12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
